--- a/artfynd/A 17740-2026 artfynd.xlsx
+++ b/artfynd/A 17740-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133423936</v>
       </c>
       <c r="B2" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17740-2026 artfynd.xlsx
+++ b/artfynd/A 17740-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133423936</v>
       </c>
       <c r="B2" t="n">
-        <v>101340</v>
+        <v>101348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17740-2026 artfynd.xlsx
+++ b/artfynd/A 17740-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133423936</v>
       </c>
       <c r="B2" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17740-2026 artfynd.xlsx
+++ b/artfynd/A 17740-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133423936</v>
       </c>
       <c r="B2" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17740-2026 artfynd.xlsx
+++ b/artfynd/A 17740-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133423936</v>
       </c>
       <c r="B2" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17740-2026 artfynd.xlsx
+++ b/artfynd/A 17740-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133423936</v>
       </c>
       <c r="B2" t="n">
-        <v>101388</v>
+        <v>101403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
